--- a/artfynd/A 31129-2025 artfynd.xlsx
+++ b/artfynd/A 31129-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AZ92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217161</t>
         </is>
       </c>
     </row>
@@ -898,6 +908,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217188</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217220</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217230</t>
         </is>
       </c>
     </row>
@@ -1239,6 +1264,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217240</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1355,6 +1385,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217162</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1466,6 +1501,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217165</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1577,6 +1617,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217200</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1688,6 +1733,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217202</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1797,6 +1847,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217207</t>
         </is>
       </c>
     </row>
@@ -1914,6 +1969,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217208</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2025,6 +2085,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217210</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2136,6 +2201,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217232</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2247,6 +2317,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217234</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2363,6 +2438,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217236</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2479,6 +2559,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217238</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2595,6 +2680,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217242</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2711,6 +2801,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217244</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2827,6 +2922,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217248</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2938,6 +3038,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217269</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3049,6 +3154,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217270</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3160,6 +3270,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217194</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3269,6 +3384,11 @@
       <c r="AY24" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217192</t>
         </is>
       </c>
     </row>
@@ -3386,6 +3506,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217256</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3491,6 +3616,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217274</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3602,6 +3732,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217169</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3713,6 +3848,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217174</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3824,6 +3964,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217177</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3935,6 +4080,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217193</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4046,6 +4196,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217195</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4157,6 +4312,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217251</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4268,6 +4428,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217255</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4379,6 +4544,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217196</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4490,6 +4660,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217259</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4601,6 +4776,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217268</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4712,6 +4892,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217191</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4823,6 +5008,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217160</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4934,6 +5124,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217221</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5045,6 +5240,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217243</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5156,6 +5356,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217201</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5267,6 +5472,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217228</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5378,6 +5588,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217229</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5489,6 +5704,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217235</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5600,6 +5820,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217239</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5711,6 +5936,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217241</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5822,6 +6052,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217172</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5933,6 +6168,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217175</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6044,6 +6284,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217179</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6160,6 +6405,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217186</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6271,6 +6521,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217187</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6382,6 +6637,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217190</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6498,6 +6758,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217197</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6609,6 +6874,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217203</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6720,6 +6990,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217250</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6831,6 +7106,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217252</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6942,6 +7222,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217262</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7053,6 +7338,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217185</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7164,6 +7454,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217204</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7275,6 +7570,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217222</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7386,6 +7686,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217225</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7502,6 +7807,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217182</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7626,6 +7936,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217224</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7750,6 +8065,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217178</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7874,6 +8194,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217184</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7998,6 +8323,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217189</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8122,6 +8452,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217211</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8246,6 +8581,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217216</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8370,6 +8710,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217217</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8494,6 +8839,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217218</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8618,6 +8968,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217219</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8742,6 +9097,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217253</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8866,6 +9226,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217254</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8990,6 +9355,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217260</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9114,6 +9484,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217263</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9238,6 +9613,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217265</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9362,6 +9742,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217267</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9486,6 +9871,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217199</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9602,6 +9992,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217227</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9718,6 +10113,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217247</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9840,6 +10240,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103018453</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9965,6 +10370,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217163</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10081,6 +10491,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217164</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10209,6 +10624,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217167</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10329,6 +10749,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217212</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10449,6 +10874,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217258</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10569,6 +10999,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217264</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10685,6 +11120,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217213</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10803,6 +11243,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103013093</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10914,6 +11359,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217245</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11025,6 +11475,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217181</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11136,8 +11591,106 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217214</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31129-2025 artfynd.xlsx
+++ b/artfynd/A 31129-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135217161</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135217188</v>
       </c>
       <c r="B3" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>135217220</v>
       </c>
       <c r="B4" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135217230</v>
       </c>
       <c r="B5" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>135217240</v>
       </c>
       <c r="B6" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135217162</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>135217165</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>135217200</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>135217202</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>135217207</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>135217208</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>135217210</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>135217232</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135217234</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>135217236</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>135217238</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135217242</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>135217244</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>135217248</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>135217269</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>135217270</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>135217194</v>
       </c>
       <c r="B23" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>135217192</v>
       </c>
       <c r="B24" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>135217256</v>
       </c>
       <c r="B25" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>135217274</v>
       </c>
       <c r="B26" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>135217169</v>
       </c>
       <c r="B27" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>135217174</v>
       </c>
       <c r="B28" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>135217177</v>
       </c>
       <c r="B29" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>135217193</v>
       </c>
       <c r="B30" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>135217195</v>
       </c>
       <c r="B31" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>135217251</v>
       </c>
       <c r="B32" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>135217255</v>
       </c>
       <c r="B33" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>135217196</v>
       </c>
       <c r="B34" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>135217259</v>
       </c>
       <c r="B35" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>135217268</v>
       </c>
       <c r="B36" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>135217191</v>
       </c>
       <c r="B37" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>135217160</v>
       </c>
       <c r="B38" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>135217221</v>
       </c>
       <c r="B39" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>135217243</v>
       </c>
       <c r="B40" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>135217201</v>
       </c>
       <c r="B41" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>135217228</v>
       </c>
       <c r="B42" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>135217229</v>
       </c>
       <c r="B43" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>135217235</v>
       </c>
       <c r="B44" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>135217239</v>
       </c>
       <c r="B45" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>135217241</v>
       </c>
       <c r="B46" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>135217172</v>
       </c>
       <c r="B47" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>135217175</v>
       </c>
       <c r="B48" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>135217179</v>
       </c>
       <c r="B49" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>135217186</v>
       </c>
       <c r="B50" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>135217187</v>
       </c>
       <c r="B51" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>135217190</v>
       </c>
       <c r="B52" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>135217197</v>
       </c>
       <c r="B53" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>135217203</v>
       </c>
       <c r="B54" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>135217250</v>
       </c>
       <c r="B55" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>135217252</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>135217262</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>135217185</v>
       </c>
       <c r="B58" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>135217204</v>
       </c>
       <c r="B59" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>135217222</v>
       </c>
       <c r="B60" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>135217225</v>
       </c>
       <c r="B61" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>135217182</v>
       </c>
       <c r="B62" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>135217224</v>
       </c>
       <c r="B63" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>135217178</v>
       </c>
       <c r="B64" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>135217184</v>
       </c>
       <c r="B65" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>135217189</v>
       </c>
       <c r="B66" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>135217211</v>
       </c>
       <c r="B67" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>135217216</v>
       </c>
       <c r="B68" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>135217217</v>
       </c>
       <c r="B69" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>135217218</v>
       </c>
       <c r="B70" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>135217219</v>
       </c>
       <c r="B71" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>135217253</v>
       </c>
       <c r="B72" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>135217254</v>
       </c>
       <c r="B73" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>135217260</v>
       </c>
       <c r="B74" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>135217263</v>
       </c>
       <c r="B75" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>135217265</v>
       </c>
       <c r="B76" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>135217267</v>
       </c>
       <c r="B77" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>135217199</v>
       </c>
       <c r="B78" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>135217227</v>
       </c>
       <c r="B79" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>135217247</v>
       </c>
       <c r="B80" t="n">
-        <v>57925</v>
+        <v>57930</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>135217163</v>
       </c>
       <c r="B82" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>135217164</v>
       </c>
       <c r="B83" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>135217167</v>
       </c>
       <c r="B84" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>135217212</v>
       </c>
       <c r="B85" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>135217258</v>
       </c>
       <c r="B86" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>135217264</v>
       </c>
       <c r="B87" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>135217213</v>
       </c>
       <c r="B88" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>135217245</v>
       </c>
       <c r="B90" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>135217181</v>
       </c>
       <c r="B91" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>135217214</v>
       </c>
       <c r="B92" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 31129-2025 artfynd.xlsx
+++ b/artfynd/A 31129-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135217161</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135217188</v>
       </c>
       <c r="B3" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>135217220</v>
       </c>
       <c r="B4" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135217230</v>
       </c>
       <c r="B5" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>135217240</v>
       </c>
       <c r="B6" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135217162</v>
       </c>
       <c r="B7" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>135217165</v>
       </c>
       <c r="B8" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>135217200</v>
       </c>
       <c r="B9" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>135217202</v>
       </c>
       <c r="B10" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>135217207</v>
       </c>
       <c r="B11" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>135217208</v>
       </c>
       <c r="B12" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>135217210</v>
       </c>
       <c r="B13" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>135217232</v>
       </c>
       <c r="B14" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135217234</v>
       </c>
       <c r="B15" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>135217236</v>
       </c>
       <c r="B16" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>135217238</v>
       </c>
       <c r="B17" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135217242</v>
       </c>
       <c r="B18" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>135217244</v>
       </c>
       <c r="B19" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>135217248</v>
       </c>
       <c r="B20" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>135217269</v>
       </c>
       <c r="B21" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>135217270</v>
       </c>
       <c r="B22" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>135217194</v>
       </c>
       <c r="B23" t="n">
-        <v>89396</v>
+        <v>89423</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>135217192</v>
       </c>
       <c r="B24" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>135217256</v>
       </c>
       <c r="B25" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>135217274</v>
       </c>
       <c r="B26" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>135217169</v>
       </c>
       <c r="B27" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>135217174</v>
       </c>
       <c r="B28" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>135217177</v>
       </c>
       <c r="B29" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>135217193</v>
       </c>
       <c r="B30" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>135217195</v>
       </c>
       <c r="B31" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>135217251</v>
       </c>
       <c r="B32" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>135217255</v>
       </c>
       <c r="B33" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>135217196</v>
       </c>
       <c r="B34" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>135217259</v>
       </c>
       <c r="B35" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>135217268</v>
       </c>
       <c r="B36" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>135217191</v>
       </c>
       <c r="B37" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>135217160</v>
       </c>
       <c r="B38" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>135217221</v>
       </c>
       <c r="B39" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>135217243</v>
       </c>
       <c r="B40" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>135217201</v>
       </c>
       <c r="B41" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>135217228</v>
       </c>
       <c r="B42" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>135217229</v>
       </c>
       <c r="B43" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>135217235</v>
       </c>
       <c r="B44" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>135217239</v>
       </c>
       <c r="B45" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>135217241</v>
       </c>
       <c r="B46" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>135217172</v>
       </c>
       <c r="B47" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>135217175</v>
       </c>
       <c r="B48" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>135217179</v>
       </c>
       <c r="B49" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>135217186</v>
       </c>
       <c r="B50" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>135217187</v>
       </c>
       <c r="B51" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>135217190</v>
       </c>
       <c r="B52" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>135217197</v>
       </c>
       <c r="B53" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>135217203</v>
       </c>
       <c r="B54" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>135217250</v>
       </c>
       <c r="B55" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>135217252</v>
       </c>
       <c r="B56" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>135217262</v>
       </c>
       <c r="B57" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>135217185</v>
       </c>
       <c r="B58" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>135217204</v>
       </c>
       <c r="B59" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>135217222</v>
       </c>
       <c r="B60" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>135217225</v>
       </c>
       <c r="B61" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>135217181</v>
       </c>
       <c r="B91" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>135217214</v>
       </c>
       <c r="B92" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 31129-2025 artfynd.xlsx
+++ b/artfynd/A 31129-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135217161</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135217188</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>135217220</v>
       </c>
       <c r="B4" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135217230</v>
       </c>
       <c r="B5" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>135217240</v>
       </c>
       <c r="B6" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>135217194</v>
       </c>
       <c r="B23" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>135217192</v>
       </c>
       <c r="B24" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>135217256</v>
       </c>
       <c r="B25" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>135217274</v>
       </c>
       <c r="B26" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>135217169</v>
       </c>
       <c r="B27" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>135217174</v>
       </c>
       <c r="B28" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>135217177</v>
       </c>
       <c r="B29" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>135217193</v>
       </c>
       <c r="B30" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>135217195</v>
       </c>
       <c r="B31" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>135217251</v>
       </c>
       <c r="B32" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>135217255</v>
       </c>
       <c r="B33" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>135217196</v>
       </c>
       <c r="B34" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>135217259</v>
       </c>
       <c r="B35" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>135217268</v>
       </c>
       <c r="B36" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>135217160</v>
       </c>
       <c r="B38" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>135217221</v>
       </c>
       <c r="B39" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>135217243</v>
       </c>
       <c r="B40" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>135217201</v>
       </c>
       <c r="B41" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>135217228</v>
       </c>
       <c r="B42" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>135217229</v>
       </c>
       <c r="B43" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>135217235</v>
       </c>
       <c r="B44" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>135217239</v>
       </c>
       <c r="B45" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>135217241</v>
       </c>
       <c r="B46" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>135217181</v>
       </c>
       <c r="B91" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
